--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/olderyoungersister.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/olderyoungersister.xlsx
@@ -417,7 +417,7 @@
     <t xml:space="preserve">ルビナスの盾</t>
   </si>
   <si>
-    <t xml:space="preserve">A rubinus shield.</t>
+    <t xml:space="preserve">A rubynus shield.</t>
   </si>
   <si>
     <t xml:space="preserve">エーテルの盾</t>
